--- a/databank.xlsx
+++ b/databank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serwis\Downloads\GASLOGISTIK_MAP_STAGE14_FILTERS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9199366E-364A-4DD2-AAC3-56A515526DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5346BF-4F78-4388-A8A1-ED9B40213AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="736" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29550,7 +29550,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E233C6F2-D33B-48CB-A397-C6257B17C211}">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="5" customWidth="1"/>
@@ -29559,10 +29559,12 @@
     <col min="4" max="4" width="19.109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="14.5546875" style="5" customWidth="1"/>
     <col min="6" max="6" width="29.44140625" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="5"/>
+    <col min="7" max="9" width="8.88671875" style="5"/>
+    <col min="10" max="10" width="18.21875" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" s="9" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -29580,7 +29582,7 @@
       </c>
       <c r="F1" s="10"/>
     </row>
-    <row r="2" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -29591,11 +29593,14 @@
         <v>10326</v>
       </c>
       <c r="D2" s="31">
+        <v>46198</v>
+      </c>
+      <c r="E2" s="32"/>
+      <c r="J2" s="31">
         <v>46205</v>
       </c>
-      <c r="E2" s="32"/>
-    </row>
-    <row r="3" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="23">
         <v>2</v>
       </c>
@@ -29610,7 +29615,7 @@
       </c>
       <c r="E3" s="32"/>
     </row>
-    <row r="4" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="23">
         <v>3</v>
       </c>
@@ -29625,7 +29630,7 @@
       </c>
       <c r="E4" s="32"/>
     </row>
-    <row r="5" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="23">
         <v>4</v>
       </c>
@@ -29640,7 +29645,7 @@
       </c>
       <c r="E5" s="18"/>
     </row>
-    <row r="6" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="23">
         <v>5</v>
       </c>
@@ -29655,7 +29660,7 @@
       </c>
       <c r="E6" s="18"/>
     </row>
-    <row r="7" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A7" s="23">
         <v>6</v>
       </c>
@@ -29670,7 +29675,7 @@
       </c>
       <c r="E7" s="18"/>
     </row>
-    <row r="8" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A8" s="23">
         <v>7</v>
       </c>
@@ -29685,7 +29690,7 @@
       </c>
       <c r="E8" s="18"/>
     </row>
-    <row r="9" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A9" s="23">
         <v>8</v>
       </c>
@@ -29700,7 +29705,7 @@
       </c>
       <c r="E9" s="18"/>
     </row>
-    <row r="10" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A10" s="23">
         <v>9</v>
       </c>
@@ -29715,7 +29720,7 @@
       </c>
       <c r="E10" s="18"/>
     </row>
-    <row r="11" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A11" s="23">
         <v>10</v>
       </c>
@@ -29730,7 +29735,7 @@
       </c>
       <c r="E11" s="32"/>
     </row>
-    <row r="12" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="23">
         <v>11</v>
       </c>
@@ -29745,7 +29750,7 @@
       </c>
       <c r="E12" s="18"/>
     </row>
-    <row r="13" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A13" s="23">
         <v>12</v>
       </c>
@@ -29760,7 +29765,7 @@
       </c>
       <c r="E13" s="18"/>
     </row>
-    <row r="14" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A14" s="23">
         <v>13</v>
       </c>
@@ -29775,7 +29780,7 @@
       </c>
       <c r="E14" s="18"/>
     </row>
-    <row r="15" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A15" s="23">
         <v>14</v>
       </c>
@@ -29790,7 +29795,7 @@
       </c>
       <c r="E15" s="18"/>
     </row>
-    <row r="16" spans="1:6" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" s="10" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A16" s="23">
         <v>15</v>
       </c>

--- a/databank.xlsx
+++ b/databank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serwis\Downloads\GASLOGISTIK_MAP_STAGE14_FILTERS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D5346BF-4F78-4388-A8A1-ED9B40213AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3C5581-809E-4D14-B9E9-D97348042963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="736" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29593,7 +29593,7 @@
         <v>10326</v>
       </c>
       <c r="D2" s="31">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="E2" s="32"/>
       <c r="J2" s="31">

--- a/databank.xlsx
+++ b/databank.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serwis\Downloads\GASLOGISTIK_MAP_STAGE14_FILTERS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD6A077-D867-4B5F-83B1-AAE446064F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09B4324-9899-4382-AB58-5B71FAD5ECE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="736" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Admin" sheetId="7" r:id="rId1"/>
     <sheet name="Miasta" sheetId="2" r:id="rId2"/>
-    <sheet name="Relacje" sheetId="11" r:id="rId3"/>
-    <sheet name="TRUCKS" sheetId="10" r:id="rId4"/>
-    <sheet name="TANKTRAILERS" sheetId="9" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="1" r:id="rId6"/>
-    <sheet name="Historia" sheetId="5" r:id="rId7"/>
-    <sheet name="Kontakt" sheetId="8" r:id="rId8"/>
+    <sheet name="ADDRESSES" sheetId="12" r:id="rId3"/>
+    <sheet name="Relacje" sheetId="11" r:id="rId4"/>
+    <sheet name="TRUCKS" sheetId="10" r:id="rId5"/>
+    <sheet name="TANKTRAILERS" sheetId="9" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="1" r:id="rId7"/>
+    <sheet name="Historia" sheetId="5" r:id="rId8"/>
+    <sheet name="Kontakt" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TANKTRAILERS!$D$1:$D$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TRUCKS!$D$1:$D$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">TANKTRAILERS!$D$1:$D$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TRUCKS!$D$1:$D$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="345">
   <si>
     <t>ID</t>
   </si>
@@ -3174,6 +3175,895 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF9DBD8-F382-4A22-AE2C-BA5D5E11EAB2}">
+  <dimension ref="A1:E59"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.77734375" style="42" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="63.88671875" customWidth="1"/>
+    <col min="4" max="4" width="21.21875" customWidth="1"/>
+    <col min="5" max="5" width="20.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="52" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="47">
+        <v>1</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="39">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>327</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="E3" s="35" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="39">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>323</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="39">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="39">
+        <v>5</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="39">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>330</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="39">
+        <v>7</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="39">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>332</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="39">
+        <v>9</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>333</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="39">
+        <v>10</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>334</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="35" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="39">
+        <v>11</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>335</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="39">
+        <v>12</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="39">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="36"/>
+      <c r="D14" s="35" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="39">
+        <v>14</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="36"/>
+      <c r="D15" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="39">
+        <v>15</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="36"/>
+      <c r="D16" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="39">
+        <v>16</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="36"/>
+      <c r="D17" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="35" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="39">
+        <v>17</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="36"/>
+      <c r="D18" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="39">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="36"/>
+      <c r="D19" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="39">
+        <v>19</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="36"/>
+      <c r="D20" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="39">
+        <v>20</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="36"/>
+      <c r="D21" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="39">
+        <v>21</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="36"/>
+      <c r="D22" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="39">
+        <v>22</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="39">
+        <v>23</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="39">
+        <v>24</v>
+      </c>
+      <c r="B25" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="36"/>
+      <c r="D25" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="35" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="39">
+        <v>25</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C26" s="36"/>
+      <c r="D26" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="39">
+        <v>26</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="36"/>
+      <c r="D27" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" s="35" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="39">
+        <v>27</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="36"/>
+      <c r="D28" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="39">
+        <v>28</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="36"/>
+      <c r="D29" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="E29" s="35" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="39">
+        <v>29</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="36"/>
+      <c r="D30" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="39">
+        <v>30</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="36"/>
+      <c r="D31" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="39">
+        <v>31</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="D32" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="39">
+        <v>32</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="35" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="39">
+        <v>33</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="36"/>
+      <c r="D34" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="35" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="39">
+        <v>34</v>
+      </c>
+      <c r="B35" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="36"/>
+      <c r="D35" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="E35" s="35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="39">
+        <v>35</v>
+      </c>
+      <c r="B36" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="36"/>
+      <c r="D36" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" s="35" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="39">
+        <v>36</v>
+      </c>
+      <c r="B37" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="36"/>
+      <c r="D37" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="E37" s="35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="39">
+        <v>37</v>
+      </c>
+      <c r="B38" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" s="35" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="36"/>
+      <c r="D39" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="39">
+        <v>39</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="36"/>
+      <c r="D40" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E40" s="35" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="39">
+        <v>40</v>
+      </c>
+      <c r="B41" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="36"/>
+      <c r="D41" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="E41" s="35" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="39">
+        <v>41</v>
+      </c>
+      <c r="B42" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="36"/>
+      <c r="D42" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="39">
+        <v>42</v>
+      </c>
+      <c r="B43" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="36"/>
+      <c r="D43" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E43" s="35" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="39">
+        <v>43</v>
+      </c>
+      <c r="B44" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="36"/>
+      <c r="D44" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="39">
+        <v>44</v>
+      </c>
+      <c r="B45" s="35" t="s">
+        <v>130</v>
+      </c>
+      <c r="C45" s="36"/>
+      <c r="D45" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="35" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="39">
+        <v>45</v>
+      </c>
+      <c r="B46" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" s="36"/>
+      <c r="D46" s="35" t="s">
+        <v>140</v>
+      </c>
+      <c r="E46" s="35" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="39">
+        <v>46</v>
+      </c>
+      <c r="B47" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="36"/>
+      <c r="D47" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="E47" s="35" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="39">
+        <v>47</v>
+      </c>
+      <c r="B48" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="C48" s="36"/>
+      <c r="D48" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" s="35" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="39">
+        <v>48</v>
+      </c>
+      <c r="B49" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C49" s="36"/>
+      <c r="D49" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="39">
+        <v>49</v>
+      </c>
+      <c r="B50" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="36"/>
+      <c r="D50" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" s="35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="39">
+        <v>50</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="36"/>
+      <c r="D51" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="35" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="39">
+        <v>51</v>
+      </c>
+      <c r="B52" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="36"/>
+      <c r="D52" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="39">
+        <v>52</v>
+      </c>
+      <c r="B53" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="36"/>
+      <c r="D53" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="39">
+        <v>53</v>
+      </c>
+      <c r="B54" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="36"/>
+      <c r="D54" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="E54" s="35" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="39">
+        <v>54</v>
+      </c>
+      <c r="B55" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" s="36"/>
+      <c r="D55" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="E55" s="35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="40">
+        <v>55</v>
+      </c>
+      <c r="B56" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="38"/>
+      <c r="D56" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="37" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="41"/>
+      <c r="B59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050142BD-5747-4115-9179-CEFB04077301}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -40561,7 +41451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{217A78BB-1CC5-468F-B159-5463F3A61CCA}">
   <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -41208,7 +42098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E233C6F2-D33B-48CB-A397-C6257B17C211}">
   <dimension ref="A1:J41"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -41870,7 +42760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -41882,7 +42772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -41961,7 +42851,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D604C46D-5742-4584-8855-51C644D904D9}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>

--- a/databank.xlsx
+++ b/databank.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serwis\Downloads\GASLOGISTIK_MAP_STAGE14_FILTERS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09B4324-9899-4382-AB58-5B71FAD5ECE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F6FB9D-8125-4CCE-869A-EFFED6CD2D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="736" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Admin" sheetId="7" r:id="rId1"/>
-    <sheet name="Miasta" sheetId="2" r:id="rId2"/>
+    <sheet name="ADMIN" sheetId="7" r:id="rId1"/>
+    <sheet name="CITIES" sheetId="2" r:id="rId2"/>
     <sheet name="ADDRESSES" sheetId="12" r:id="rId3"/>
-    <sheet name="Relacje" sheetId="11" r:id="rId4"/>
+    <sheet name="RELATIONS" sheetId="11" r:id="rId4"/>
     <sheet name="TRUCKS" sheetId="10" r:id="rId5"/>
     <sheet name="TANKTRAILERS" sheetId="9" r:id="rId6"/>
-    <sheet name="Dashboard" sheetId="1" r:id="rId7"/>
-    <sheet name="Historia" sheetId="5" r:id="rId8"/>
-    <sheet name="Kontakt" sheetId="8" r:id="rId9"/>
+    <sheet name="DASHBOARD" sheetId="1" r:id="rId7"/>
+    <sheet name="HISTORY" sheetId="5" r:id="rId8"/>
+    <sheet name="CONTACT" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">TANKTRAILERS!$D$1:$D$37</definedName>

--- a/databank.xlsx
+++ b/databank.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serwis\Downloads\GASLOGISTIK_MAP_STAGE14_FILTERS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Serwis\Desktop\Nowy folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F6FB9D-8125-4CCE-869A-EFFED6CD2D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB2F2E9-7939-4BF7-BED3-26A392495838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="736" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ADMIN" sheetId="7" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3162" uniqueCount="353">
   <si>
     <t>ID</t>
   </si>
@@ -1081,6 +1081,30 @@
   <si>
     <t>Korczowa</t>
   </si>
+  <si>
+    <t>Henri Victor Wolvensstraat 3, 8380 Brugge, Belgia</t>
+  </si>
+  <si>
+    <t>3.216211098061301</t>
+  </si>
+  <si>
+    <t>51.35284621948511</t>
+  </si>
+  <si>
+    <t>4.072266813591814</t>
+  </si>
+  <si>
+    <t>51.97398435797171</t>
+  </si>
+  <si>
+    <t>Gate Rotterdam</t>
+  </si>
+  <si>
+    <t>Zeebruge Belgium</t>
+  </si>
+  <si>
+    <t>Maasvlakteweg 991, 3199 LZ Maasvlakte Rotterdam, Holandia</t>
+  </si>
 </sst>
 </file>
 
@@ -1514,7 +1538,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1651,6 +1675,16 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Dziesiętny 2" xfId="2" xr:uid="{ED72E06B-5D99-4473-A1AE-3B7ACE627A9F}"/>
@@ -3186,48 +3220,48 @@
     <col min="5" max="5" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="56" t="s">
         <v>170</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="57" t="s">
         <v>265</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="56" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="47">
+      <c r="A2" s="56">
         <v>1</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="35" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="39">
+      <c r="A3" s="56">
         <v>2</v>
       </c>
       <c r="B3" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="34" t="s">
         <v>327</v>
       </c>
       <c r="D3" s="35" t="s">
@@ -3238,13 +3272,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="39">
+      <c r="A4" s="56">
         <v>3</v>
       </c>
       <c r="B4" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="34" t="s">
         <v>323</v>
       </c>
       <c r="D4" s="35" t="s">
@@ -3255,13 +3289,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39">
+      <c r="A5" s="56">
         <v>4</v>
       </c>
       <c r="B5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="34" t="s">
         <v>326</v>
       </c>
       <c r="D5" s="35" t="s">
@@ -3272,13 +3306,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+      <c r="A6" s="56">
         <v>5</v>
       </c>
       <c r="B6" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C6" s="34" t="s">
         <v>329</v>
       </c>
       <c r="D6" s="35" t="s">
@@ -3289,13 +3323,13 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="39">
+      <c r="A7" s="56">
         <v>6</v>
       </c>
       <c r="B7" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C7" s="34" t="s">
         <v>330</v>
       </c>
       <c r="D7" s="35" t="s">
@@ -3306,13 +3340,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="39">
+      <c r="A8" s="56">
         <v>7</v>
       </c>
       <c r="B8" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="34" t="s">
         <v>331</v>
       </c>
       <c r="D8" s="35" t="s">
@@ -3323,13 +3357,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="39">
+      <c r="A9" s="56">
         <v>8</v>
       </c>
       <c r="B9" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="34" t="s">
         <v>332</v>
       </c>
       <c r="D9" s="35" t="s">
@@ -3340,13 +3374,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="39">
+      <c r="A10" s="56">
         <v>9</v>
       </c>
       <c r="B10" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="34" t="s">
         <v>333</v>
       </c>
       <c r="D10" s="35" t="s">
@@ -3357,13 +3391,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="39">
+      <c r="A11" s="56">
         <v>10</v>
       </c>
       <c r="B11" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="34" t="s">
         <v>334</v>
       </c>
       <c r="D11" s="35" t="s">
@@ -3374,13 +3408,13 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="39">
+      <c r="A12" s="56">
         <v>11</v>
       </c>
       <c r="B12" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="34" t="s">
         <v>335</v>
       </c>
       <c r="D12" s="35" t="s">
@@ -3391,13 +3425,13 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="39">
+      <c r="A13" s="56">
         <v>12</v>
       </c>
       <c r="B13" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="34" t="s">
         <v>336</v>
       </c>
       <c r="D13" s="35" t="s">
@@ -3408,13 +3442,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="56">
         <v>13</v>
       </c>
       <c r="B14" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="C14" s="36"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="35" t="s">
         <v>153</v>
       </c>
@@ -3423,13 +3457,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="39">
+      <c r="A15" s="56">
         <v>14</v>
       </c>
       <c r="B15" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="36"/>
+      <c r="C15" s="34"/>
       <c r="D15" s="35" t="s">
         <v>37</v>
       </c>
@@ -3438,13 +3472,13 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="39">
+      <c r="A16" s="56">
         <v>15</v>
       </c>
       <c r="B16" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="36"/>
+      <c r="C16" s="34"/>
       <c r="D16" s="35" t="s">
         <v>37</v>
       </c>
@@ -3453,13 +3487,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="39">
+      <c r="A17" s="56">
         <v>16</v>
       </c>
       <c r="B17" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="36"/>
+      <c r="C17" s="34"/>
       <c r="D17" s="35" t="s">
         <v>25</v>
       </c>
@@ -3468,13 +3502,13 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="39">
+      <c r="A18" s="56">
         <v>17</v>
       </c>
       <c r="B18" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="36"/>
+      <c r="C18" s="34"/>
       <c r="D18" s="35" t="s">
         <v>28</v>
       </c>
@@ -3483,13 +3517,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="39">
+      <c r="A19" s="56">
         <v>18</v>
       </c>
       <c r="B19" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="36"/>
+      <c r="C19" s="34"/>
       <c r="D19" s="35" t="s">
         <v>31</v>
       </c>
@@ -3498,13 +3532,13 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="39">
+      <c r="A20" s="56">
         <v>19</v>
       </c>
       <c r="B20" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="36"/>
+      <c r="C20" s="34"/>
       <c r="D20" s="35" t="s">
         <v>50</v>
       </c>
@@ -3513,13 +3547,13 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="39">
+      <c r="A21" s="56">
         <v>20</v>
       </c>
       <c r="B21" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="36"/>
+      <c r="C21" s="34"/>
       <c r="D21" s="35" t="s">
         <v>53</v>
       </c>
@@ -3528,13 +3562,13 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="39">
+      <c r="A22" s="56">
         <v>21</v>
       </c>
       <c r="B22" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="36"/>
+      <c r="C22" s="34"/>
       <c r="D22" s="35" t="s">
         <v>56</v>
       </c>
@@ -3543,13 +3577,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="39">
+      <c r="A23" s="56">
         <v>22</v>
       </c>
       <c r="B23" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="36"/>
+      <c r="C23" s="34"/>
       <c r="D23" s="35" t="s">
         <v>59</v>
       </c>
@@ -3558,13 +3592,13 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="39">
+      <c r="A24" s="56">
         <v>23</v>
       </c>
       <c r="B24" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="36"/>
+      <c r="C24" s="34"/>
       <c r="D24" s="35" t="s">
         <v>65</v>
       </c>
@@ -3573,13 +3607,13 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="39">
+      <c r="A25" s="56">
         <v>24</v>
       </c>
       <c r="B25" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="36"/>
+      <c r="C25" s="34"/>
       <c r="D25" s="35" t="s">
         <v>68</v>
       </c>
@@ -3588,13 +3622,13 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="39">
+      <c r="A26" s="56">
         <v>25</v>
       </c>
       <c r="B26" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="36"/>
+      <c r="C26" s="34"/>
       <c r="D26" s="35" t="s">
         <v>71</v>
       </c>
@@ -3603,13 +3637,13 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="39">
+      <c r="A27" s="56">
         <v>26</v>
       </c>
       <c r="B27" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="36"/>
+      <c r="C27" s="34"/>
       <c r="D27" s="35" t="s">
         <v>80</v>
       </c>
@@ -3618,13 +3652,13 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="39">
+      <c r="A28" s="56">
         <v>27</v>
       </c>
       <c r="B28" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="C28" s="36"/>
+      <c r="C28" s="34"/>
       <c r="D28" s="35" t="s">
         <v>83</v>
       </c>
@@ -3633,13 +3667,13 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="39">
+      <c r="A29" s="56">
         <v>28</v>
       </c>
       <c r="B29" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="C29" s="36"/>
+      <c r="C29" s="34"/>
       <c r="D29" s="35" t="s">
         <v>86</v>
       </c>
@@ -3648,13 +3682,13 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="39">
+      <c r="A30" s="56">
         <v>29</v>
       </c>
       <c r="B30" s="35" t="s">
         <v>88</v>
       </c>
-      <c r="C30" s="36"/>
+      <c r="C30" s="34"/>
       <c r="D30" s="35" t="s">
         <v>89</v>
       </c>
@@ -3663,13 +3697,13 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="39">
+      <c r="A31" s="56">
         <v>30</v>
       </c>
       <c r="B31" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="36"/>
+      <c r="C31" s="34"/>
       <c r="D31" s="35" t="s">
         <v>92</v>
       </c>
@@ -3678,13 +3712,13 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="39">
+      <c r="A32" s="56">
         <v>31</v>
       </c>
       <c r="B32" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="C32" s="36"/>
+      <c r="C32" s="34"/>
       <c r="D32" s="35" t="s">
         <v>94</v>
       </c>
@@ -3693,13 +3727,13 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="39">
+      <c r="A33" s="56">
         <v>32</v>
       </c>
       <c r="B33" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="36"/>
+      <c r="C33" s="34"/>
       <c r="D33" s="35" t="s">
         <v>97</v>
       </c>
@@ -3708,13 +3742,13 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="39">
+      <c r="A34" s="56">
         <v>33</v>
       </c>
       <c r="B34" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="36"/>
+      <c r="C34" s="34"/>
       <c r="D34" s="35" t="s">
         <v>100</v>
       </c>
@@ -3723,13 +3757,13 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="39">
+      <c r="A35" s="56">
         <v>34</v>
       </c>
       <c r="B35" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="36"/>
+      <c r="C35" s="34"/>
       <c r="D35" s="35" t="s">
         <v>103</v>
       </c>
@@ -3738,13 +3772,13 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="39">
+      <c r="A36" s="56">
         <v>35</v>
       </c>
       <c r="B36" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="C36" s="36"/>
+      <c r="C36" s="34"/>
       <c r="D36" s="35" t="s">
         <v>106</v>
       </c>
@@ -3753,13 +3787,13 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="39">
+      <c r="A37" s="56">
         <v>36</v>
       </c>
       <c r="B37" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="C37" s="36"/>
+      <c r="C37" s="34"/>
       <c r="D37" s="35" t="s">
         <v>109</v>
       </c>
@@ -3768,13 +3802,13 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="39">
+      <c r="A38" s="56">
         <v>37</v>
       </c>
       <c r="B38" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="36"/>
+      <c r="C38" s="34"/>
       <c r="D38" s="35" t="s">
         <v>134</v>
       </c>
@@ -3783,13 +3817,13 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="39">
+      <c r="A39" s="56">
         <v>38</v>
       </c>
       <c r="B39" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="36"/>
+      <c r="C39" s="34"/>
       <c r="D39" s="35" t="s">
         <v>115</v>
       </c>
@@ -3798,13 +3832,13 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="39">
+      <c r="A40" s="56">
         <v>39</v>
       </c>
       <c r="B40" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="C40" s="36"/>
+      <c r="C40" s="34"/>
       <c r="D40" s="35" t="s">
         <v>137</v>
       </c>
@@ -3813,13 +3847,13 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="39">
+      <c r="A41" s="56">
         <v>40</v>
       </c>
       <c r="B41" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="C41" s="36"/>
+      <c r="C41" s="34"/>
       <c r="D41" s="35" t="s">
         <v>112</v>
       </c>
@@ -3828,13 +3862,13 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="39">
+      <c r="A42" s="56">
         <v>41</v>
       </c>
       <c r="B42" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="36"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="35" t="s">
         <v>118</v>
       </c>
@@ -3843,13 +3877,13 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="39">
+      <c r="A43" s="56">
         <v>42</v>
       </c>
       <c r="B43" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="C43" s="36"/>
+      <c r="C43" s="34"/>
       <c r="D43" s="35" t="s">
         <v>122</v>
       </c>
@@ -3858,13 +3892,13 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="39">
+      <c r="A44" s="56">
         <v>43</v>
       </c>
       <c r="B44" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="C44" s="36"/>
+      <c r="C44" s="34"/>
       <c r="D44" s="35" t="s">
         <v>125</v>
       </c>
@@ -3873,13 +3907,13 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="39">
+      <c r="A45" s="56">
         <v>44</v>
       </c>
       <c r="B45" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="36"/>
+      <c r="C45" s="34"/>
       <c r="D45" s="35" t="s">
         <v>131</v>
       </c>
@@ -3888,13 +3922,13 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="39">
+      <c r="A46" s="56">
         <v>45</v>
       </c>
       <c r="B46" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="36"/>
+      <c r="C46" s="34"/>
       <c r="D46" s="35" t="s">
         <v>140</v>
       </c>
@@ -3903,13 +3937,13 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="39">
+      <c r="A47" s="56">
         <v>46</v>
       </c>
       <c r="B47" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="36"/>
+      <c r="C47" s="34"/>
       <c r="D47" s="35" t="s">
         <v>146</v>
       </c>
@@ -3918,13 +3952,13 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="39">
+      <c r="A48" s="56">
         <v>47</v>
       </c>
       <c r="B48" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="C48" s="36"/>
+      <c r="C48" s="34"/>
       <c r="D48" s="35" t="s">
         <v>156</v>
       </c>
@@ -3933,13 +3967,13 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="39">
+      <c r="A49" s="56">
         <v>48</v>
       </c>
       <c r="B49" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="36"/>
+      <c r="C49" s="34"/>
       <c r="D49" s="35" t="s">
         <v>62</v>
       </c>
@@ -3948,13 +3982,13 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="39">
+      <c r="A50" s="56">
         <v>49</v>
       </c>
       <c r="B50" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C50" s="36"/>
+      <c r="C50" s="34"/>
       <c r="D50" s="35" t="s">
         <v>34</v>
       </c>
@@ -3963,13 +3997,13 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="39">
+      <c r="A51" s="56">
         <v>50</v>
       </c>
       <c r="B51" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="36"/>
+      <c r="C51" s="34"/>
       <c r="D51" s="35" t="s">
         <v>74</v>
       </c>
@@ -3978,13 +4012,13 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="39">
+      <c r="A52" s="56">
         <v>51</v>
       </c>
       <c r="B52" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="C52" s="36"/>
+      <c r="C52" s="34"/>
       <c r="D52" s="35" t="s">
         <v>77</v>
       </c>
@@ -3993,13 +4027,13 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="39">
+      <c r="A53" s="56">
         <v>52</v>
       </c>
       <c r="B53" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="C53" s="36"/>
+      <c r="C53" s="34"/>
       <c r="D53" s="35" t="s">
         <v>128</v>
       </c>
@@ -4008,13 +4042,13 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="39">
+      <c r="A54" s="56">
         <v>53</v>
       </c>
       <c r="B54" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C54" s="36"/>
+      <c r="C54" s="34"/>
       <c r="D54" s="35" t="s">
         <v>41</v>
       </c>
@@ -4023,13 +4057,13 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="39">
+      <c r="A55" s="56">
         <v>54</v>
       </c>
       <c r="B55" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="C55" s="36"/>
+      <c r="C55" s="34"/>
       <c r="D55" s="35" t="s">
         <v>44</v>
       </c>
@@ -4037,19 +4071,53 @@
         <v>45</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="40">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="56">
         <v>55</v>
       </c>
-      <c r="B56" s="37" t="s">
+      <c r="B56" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="38"/>
-      <c r="D56" s="37" t="s">
+      <c r="C56" s="34"/>
+      <c r="D56" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="E56" s="37" t="s">
+      <c r="E56" s="35" t="s">
         <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="58">
+        <v>56</v>
+      </c>
+      <c r="B57" s="59" t="s">
+        <v>351</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="E57" s="34" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="E58" s="34" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
